--- a/assets/plantilla_notas_tablero_docente.xlsx
+++ b/assets/plantilla_notas_tablero_docente.xlsx
@@ -426,7 +426,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>1. En la hoja "Curso" escribe los datos de tu asignatura, los pesos de cada corte (deben sumar 100) y la intensidad horaria total.</v>
+        <v>1. En la hoja "Curso" escribe los datos de tu asignatura, los pesos de cada corte (deben sumar 100) y la intensidad horaria total según el microcurrículo (32, 48 o 64 horas; equivale a 2, 3 o 4 horas semanales).</v>
       </c>
     </row>
     <row r="6">
@@ -545,7 +545,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Intensidad horaria total (horas)</v>
+        <v>Intensidad horaria total (32, 48 o 64 horas)</v>
       </c>
       <c r="B9">
         <v>48</v>
